--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>107.5</v>
+        <v>115.75</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6043,7 +6043,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>101.5</v>
+        <v>107.5</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6074,7 +6074,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>103.27</v>
+        <v>111.91</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6105,7 +6105,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>104.24</v>
+        <v>112.88</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6167,7 +6167,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>86.90000000000001</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6193,7 +6193,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>103</v>
+        <v>110.75</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6219,7 +6219,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>85.5</v>
+        <v>92</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6245,7 +6245,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>46</v>
+        <v>46.39</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6271,7 +6271,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>70.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>2</v>
@@ -6297,7 +6297,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>69.84999999999999</v>
+        <v>70.44</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6323,7 +6323,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>63.76</v>
+        <v>64.61</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6349,7 +6349,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>40.7</v>
+        <v>41.55</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6375,7 +6375,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6401,7 +6401,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>56.65</v>
+        <v>57.5</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6427,7 +6427,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>52.65</v>
+        <v>53.22</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indice" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OMIE_20" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OMIE_6P" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OMIP" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PQ_Mensual" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PQ_Diario" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PQ_Mensual6P" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PQ_OMIP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Indice" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OMIE_20" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="OMIE_6P" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="OMIP" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="PQ_Mensual" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="PQ_Diario" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="PQ_Mensual6P" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="PQ_OMIP" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1287,7 +1287,7 @@
         <v>4</v>
       </c>
       <c r="W10" s="20" t="n">
-        <v>118.91</v>
+        <v>118.92</v>
       </c>
       <c r="X10" s="20" t="n">
         <v>199.47</v>
@@ -1724,15 +1724,15 @@
         <v/>
       </c>
       <c r="I17" s="17">
-        <f>IF($H17="","",IFERROR(VLOOKUP($H17,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H17="","",IFERROR(VLOOKUP($H17,PQ_Diario!$A:$D,2,0),V17))</f>
         <v/>
       </c>
       <c r="J17" s="17">
-        <f>IF($H17="","",IFERROR(VLOOKUP($H17,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H17="","",IFERROR(VLOOKUP($H17,PQ_Diario!$A:$D,3,0),W17))</f>
         <v/>
       </c>
       <c r="K17" s="17">
-        <f>IF($H17="","",IFERROR(VLOOKUP($H17,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H17="","",IFERROR(VLOOKUP($H17,PQ_Diario!$A:$D,4,0),X17))</f>
         <v/>
       </c>
       <c r="Q17" s="18">
@@ -1751,6 +1751,15 @@
       </c>
       <c r="U17" s="19" t="n">
         <v>0.06365</v>
+      </c>
+      <c r="V17" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="W17" s="20" t="n">
+        <v>135.31</v>
+      </c>
+      <c r="X17" s="20" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="18">

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1791,15 +1791,15 @@
         <v/>
       </c>
       <c r="I18" s="17">
-        <f>IF($H18="","",IFERROR(VLOOKUP($H18,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H18="","",IFERROR(VLOOKUP($H18,PQ_Diario!$A:$D,2,0),V18))</f>
         <v/>
       </c>
       <c r="J18" s="17">
-        <f>IF($H18="","",IFERROR(VLOOKUP($H18,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H18="","",IFERROR(VLOOKUP($H18,PQ_Diario!$A:$D,3,0),W18))</f>
         <v/>
       </c>
       <c r="K18" s="17">
-        <f>IF($H18="","",IFERROR(VLOOKUP($H18,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H18="","",IFERROR(VLOOKUP($H18,PQ_Diario!$A:$D,4,0),X18))</f>
         <v/>
       </c>
       <c r="Q18" s="21">
@@ -1818,6 +1818,15 @@
       </c>
       <c r="U18" s="19" t="n">
         <v>0.06423</v>
+      </c>
+      <c r="V18" s="20" t="n">
+        <v>21</v>
+      </c>
+      <c r="W18" s="20" t="n">
+        <v>138.9</v>
+      </c>
+      <c r="X18" s="20" t="n">
+        <v>268.97</v>
       </c>
     </row>
     <row r="19">
@@ -5966,7 +5975,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6021,7 +6030,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>115.75</v>
+        <v>110.5</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6052,7 +6061,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>107.5</v>
+        <v>106.5</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6083,7 +6092,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>111.91</v>
+        <v>107.51</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6114,7 +6123,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>112.88</v>
+        <v>108.47</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6145,7 +6154,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>98.56</v>
+        <v>96.56</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6176,7 +6185,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>93.40000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6202,7 +6211,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>110.75</v>
+        <v>107.49</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6228,7 +6237,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6254,7 +6263,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>46.39</v>
+        <v>47.02</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6280,7 +6289,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>71.40000000000001</v>
+        <v>72.37</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>2</v>
@@ -6306,7 +6315,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>70.44</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6332,7 +6341,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>64.61</v>
+        <v>64.11</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6358,7 +6367,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>41.55</v>
+        <v>41.05</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6384,7 +6393,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>70</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6410,7 +6419,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>57.5</v>
+        <v>57</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6436,7 +6445,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>53.22</v>
+        <v>54</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1858,15 +1858,15 @@
         <v/>
       </c>
       <c r="I19" s="17">
-        <f>IF($H19="","",IFERROR(VLOOKUP($H19,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H19="","",IFERROR(VLOOKUP($H19,PQ_Diario!$A:$D,2,0),V19))</f>
         <v/>
       </c>
       <c r="J19" s="17">
-        <f>IF($H19="","",IFERROR(VLOOKUP($H19,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H19="","",IFERROR(VLOOKUP($H19,PQ_Diario!$A:$D,3,0),W19))</f>
         <v/>
       </c>
       <c r="K19" s="17">
-        <f>IF($H19="","",IFERROR(VLOOKUP($H19,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H19="","",IFERROR(VLOOKUP($H19,PQ_Diario!$A:$D,4,0),X19))</f>
         <v/>
       </c>
       <c r="S19" s="19" t="n">
@@ -1877,6 +1877,15 @@
       </c>
       <c r="U19" s="19" t="n">
         <v>0.03621</v>
+      </c>
+      <c r="V19" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="W19" s="20" t="n">
+        <v>140.09</v>
+      </c>
+      <c r="X19" s="20" t="n">
+        <v>252.5</v>
       </c>
     </row>
     <row r="20">
@@ -5975,7 +5984,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6030,7 +6039,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>110.5</v>
+        <v>112.75</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6061,7 +6070,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>106.5</v>
+        <v>108.5</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6092,7 +6101,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>107.51</v>
+        <v>109.82</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6123,7 +6132,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>108.47</v>
+        <v>110.78</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6211,7 +6220,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>107.49</v>
+        <v>109.7</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6263,7 +6272,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>47.02</v>
+        <v>47.36</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6289,7 +6298,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>72.37</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>2</v>
@@ -6315,7 +6324,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>71.40000000000001</v>
+        <v>71.92</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6341,7 +6350,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>64.11</v>
+        <v>64.66</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6367,7 +6376,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>41.05</v>
+        <v>41.6</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6393,7 +6402,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>70.15000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6419,7 +6428,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>57</v>
+        <v>57.55</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1917,15 +1917,15 @@
         <v/>
       </c>
       <c r="I20" s="17">
-        <f>IF($H20="","",IFERROR(VLOOKUP($H20,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H20="","",IFERROR(VLOOKUP($H20,PQ_Diario!$A:$D,2,0),V20))</f>
         <v/>
       </c>
       <c r="J20" s="17">
-        <f>IF($H20="","",IFERROR(VLOOKUP($H20,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H20="","",IFERROR(VLOOKUP($H20,PQ_Diario!$A:$D,3,0),W20))</f>
         <v/>
       </c>
       <c r="K20" s="17">
-        <f>IF($H20="","",IFERROR(VLOOKUP($H20,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H20="","",IFERROR(VLOOKUP($H20,PQ_Diario!$A:$D,4,0),X20))</f>
         <v/>
       </c>
       <c r="S20" s="19" t="n">
@@ -1936,6 +1936,15 @@
       </c>
       <c r="U20" s="19" t="n">
         <v>0.01494</v>
+      </c>
+      <c r="V20" s="20" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="W20" s="20" t="n">
+        <v>116.51</v>
+      </c>
+      <c r="X20" s="20" t="n">
+        <v>209.95</v>
       </c>
     </row>
     <row r="21">
@@ -5984,7 +5993,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6039,7 +6048,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>112.75</v>
+        <v>114.2</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6070,7 +6079,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>108.5</v>
+        <v>108.65</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6101,7 +6110,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>109.82</v>
+        <v>108.85</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6132,7 +6141,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>110.78</v>
+        <v>108.31</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6163,7 +6172,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>96.56</v>
+        <v>95.66</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6194,7 +6203,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>91.40000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6220,7 +6229,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>109.7</v>
+        <v>108.6</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6246,7 +6255,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>90</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6272,7 +6281,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>47.36</v>
+        <v>47.72</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6298,7 +6307,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>72.90000000000001</v>
+        <v>73.47</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>2</v>
@@ -6324,7 +6333,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>71.92</v>
+        <v>72.47</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6350,7 +6359,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>64.66</v>
+        <v>64.36</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6376,7 +6385,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>41.6</v>
+        <v>41.3</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6402,7 +6411,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>70.5</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6428,7 +6437,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>57.55</v>
+        <v>57.25</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6454,7 +6463,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>54</v>
+        <v>53.7</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1976,15 +1976,15 @@
         <v/>
       </c>
       <c r="I21" s="17">
-        <f>IF($H21="","",IFERROR(VLOOKUP($H21,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H21="","",IFERROR(VLOOKUP($H21,PQ_Diario!$A:$D,2,0),V21))</f>
         <v/>
       </c>
       <c r="J21" s="17">
-        <f>IF($H21="","",IFERROR(VLOOKUP($H21,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H21="","",IFERROR(VLOOKUP($H21,PQ_Diario!$A:$D,3,0),W21))</f>
         <v/>
       </c>
       <c r="K21" s="17">
-        <f>IF($H21="","",IFERROR(VLOOKUP($H21,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H21="","",IFERROR(VLOOKUP($H21,PQ_Diario!$A:$D,4,0),X21))</f>
         <v/>
       </c>
       <c r="S21" s="19" t="n">
@@ -1995,6 +1995,15 @@
       </c>
       <c r="U21" s="19" t="n">
         <v>0.01337</v>
+      </c>
+      <c r="V21" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" s="20" t="n">
+        <v>116.02</v>
+      </c>
+      <c r="X21" s="20" t="n">
+        <v>215.04</v>
       </c>
     </row>
     <row r="22">
@@ -5993,7 +6002,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6048,7 +6057,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>114.2</v>
+        <v>118.4</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6079,7 +6088,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>108.65</v>
+        <v>111.83</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6110,7 +6119,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>108.85</v>
+        <v>109.98</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6141,7 +6150,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>108.31</v>
+        <v>107.98</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6172,7 +6181,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>95.66</v>
+        <v>96.31</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6203,7 +6212,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>90.5</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6229,7 +6238,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>108.6</v>
+        <v>109.93</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6255,7 +6264,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>89.09999999999999</v>
+        <v>89.75</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6281,7 +6290,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>47.72</v>
+        <v>48.64</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6307,7 +6316,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>73.47</v>
+        <v>74.89</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>2</v>
@@ -6333,7 +6342,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>72.47</v>
+        <v>73.87</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6359,7 +6368,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>64.36</v>
+        <v>64.86</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6385,7 +6394,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>41.3</v>
+        <v>41.8</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6411,7 +6420,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>70.65000000000001</v>
+        <v>71.75</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6437,7 +6446,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>57.25</v>
+        <v>57.75</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2035,15 +2035,15 @@
         <v/>
       </c>
       <c r="I22" s="17">
-        <f>IF($H22="","",IFERROR(VLOOKUP($H22,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H22="","",IFERROR(VLOOKUP($H22,PQ_Diario!$A:$D,2,0),V22))</f>
         <v/>
       </c>
       <c r="J22" s="17">
-        <f>IF($H22="","",IFERROR(VLOOKUP($H22,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H22="","",IFERROR(VLOOKUP($H22,PQ_Diario!$A:$D,3,0),W22))</f>
         <v/>
       </c>
       <c r="K22" s="17">
-        <f>IF($H22="","",IFERROR(VLOOKUP($H22,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H22="","",IFERROR(VLOOKUP($H22,PQ_Diario!$A:$D,4,0),X22))</f>
         <v/>
       </c>
       <c r="S22" s="19" t="n">
@@ -2054,6 +2054,15 @@
       </c>
       <c r="U22" s="19" t="n">
         <v>0.03306</v>
+      </c>
+      <c r="V22" s="20" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="W22" s="20" t="n">
+        <v>157.35</v>
+      </c>
+      <c r="X22" s="20" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="23">
@@ -6002,7 +6011,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2094,15 +2094,15 @@
         <v/>
       </c>
       <c r="I23" s="17">
-        <f>IF($H23="","",IFERROR(VLOOKUP($H23,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H23="","",IFERROR(VLOOKUP($H23,PQ_Diario!$A:$D,2,0),V23))</f>
         <v/>
       </c>
       <c r="J23" s="17">
-        <f>IF($H23="","",IFERROR(VLOOKUP($H23,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H23="","",IFERROR(VLOOKUP($H23,PQ_Diario!$A:$D,3,0),W23))</f>
         <v/>
       </c>
       <c r="K23" s="17">
-        <f>IF($H23="","",IFERROR(VLOOKUP($H23,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H23="","",IFERROR(VLOOKUP($H23,PQ_Diario!$A:$D,4,0),X23))</f>
         <v/>
       </c>
       <c r="S23" s="19" t="n">
@@ -2113,6 +2113,15 @@
       </c>
       <c r="U23" s="19" t="n">
         <v>0.05189</v>
+      </c>
+      <c r="V23" s="20" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="W23" s="20" t="n">
+        <v>127.64</v>
+      </c>
+      <c r="X23" s="20" t="n">
+        <v>248</v>
       </c>
     </row>
     <row r="24">
@@ -6011,7 +6020,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2153,15 +2153,15 @@
         <v/>
       </c>
       <c r="I24" s="17">
-        <f>IF($H24="","",IFERROR(VLOOKUP($H24,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H24="","",IFERROR(VLOOKUP($H24,PQ_Diario!$A:$D,2,0),V24))</f>
         <v/>
       </c>
       <c r="J24" s="17">
-        <f>IF($H24="","",IFERROR(VLOOKUP($H24,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H24="","",IFERROR(VLOOKUP($H24,PQ_Diario!$A:$D,3,0),W24))</f>
         <v/>
       </c>
       <c r="K24" s="17">
-        <f>IF($H24="","",IFERROR(VLOOKUP($H24,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H24="","",IFERROR(VLOOKUP($H24,PQ_Diario!$A:$D,4,0),X24))</f>
         <v/>
       </c>
       <c r="S24" s="19" t="n">
@@ -2172,6 +2172,15 @@
       </c>
       <c r="U24" s="19" t="n">
         <v>0.07045</v>
+      </c>
+      <c r="V24" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="W24" s="20" t="n">
+        <v>127.55</v>
+      </c>
+      <c r="X24" s="20" t="n">
+        <v>216.74</v>
       </c>
     </row>
     <row r="25">
@@ -6020,7 +6029,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6075,7 +6084,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>118.4</v>
+        <v>114.95</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6106,7 +6115,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>111.83</v>
+        <v>110.5</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6137,7 +6146,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>109.98</v>
+        <v>111.07</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6168,7 +6177,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>107.98</v>
+        <v>109.06</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6199,7 +6208,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>96.31</v>
+        <v>96.56</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6230,7 +6239,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>91.15000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6256,7 +6265,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>109.93</v>
+        <v>110.2</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6282,7 +6291,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>89.75</v>
+        <v>90</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6308,7 +6317,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>48.64</v>
+        <v>49.25</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6334,7 +6343,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>74.89</v>
+        <v>73.37</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>2</v>
@@ -6360,7 +6369,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>73.87</v>
+        <v>72.36</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6386,7 +6395,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>64.86</v>
+        <v>64.45</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6412,7 +6421,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>41.8</v>
+        <v>41.39</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6438,7 +6447,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>71.75</v>
+        <v>71.2</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6464,7 +6473,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>57.75</v>
+        <v>57.34</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6490,7 +6499,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>53.7</v>
+        <v>53.29</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2212,15 +2212,15 @@
         <v/>
       </c>
       <c r="I25" s="17">
-        <f>IF($H25="","",IFERROR(VLOOKUP($H25,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H25="","",IFERROR(VLOOKUP($H25,PQ_Diario!$A:$D,2,0),V25))</f>
         <v/>
       </c>
       <c r="J25" s="17">
-        <f>IF($H25="","",IFERROR(VLOOKUP($H25,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H25="","",IFERROR(VLOOKUP($H25,PQ_Diario!$A:$D,3,0),W25))</f>
         <v/>
       </c>
       <c r="K25" s="17">
-        <f>IF($H25="","",IFERROR(VLOOKUP($H25,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H25="","",IFERROR(VLOOKUP($H25,PQ_Diario!$A:$D,4,0),X25))</f>
         <v/>
       </c>
       <c r="S25" s="19" t="n">
@@ -2231,6 +2231,15 @@
       </c>
       <c r="U25" s="19" t="n">
         <v>0.08558</v>
+      </c>
+      <c r="V25" s="20" t="n">
+        <v>46.52</v>
+      </c>
+      <c r="W25" s="20" t="n">
+        <v>138.69</v>
+      </c>
+      <c r="X25" s="20" t="n">
+        <v>202.04</v>
       </c>
     </row>
     <row r="26">
@@ -6029,7 +6038,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6084,7 +6093,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>114.95</v>
+        <v>114.5</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6115,7 +6124,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>110.5</v>
+        <v>110.35</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6146,7 +6155,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>111.07</v>
+        <v>114.78</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6177,7 +6186,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>109.06</v>
+        <v>112.45</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6265,7 +6274,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>110.2</v>
+        <v>112.5</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6317,7 +6326,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>49.25</v>
+        <v>49.74</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6343,7 +6352,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>73.37</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>2</v>
@@ -6369,7 +6378,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>72.36</v>
+        <v>73.09</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6395,7 +6404,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>64.45</v>
+        <v>64.86</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6421,7 +6430,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>41.39</v>
+        <v>41.8</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6447,7 +6456,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>71.2</v>
+        <v>71.25</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6473,7 +6482,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>57.34</v>
+        <v>57.75</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6499,7 +6508,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>53.29</v>
+        <v>53.4</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2271,15 +2271,15 @@
         <v/>
       </c>
       <c r="I26" s="17">
-        <f>IF($H26="","",IFERROR(VLOOKUP($H26,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H26="","",IFERROR(VLOOKUP($H26,PQ_Diario!$A:$D,2,0),V26))</f>
         <v/>
       </c>
       <c r="J26" s="17">
-        <f>IF($H26="","",IFERROR(VLOOKUP($H26,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H26="","",IFERROR(VLOOKUP($H26,PQ_Diario!$A:$D,3,0),W26))</f>
         <v/>
       </c>
       <c r="K26" s="17">
-        <f>IF($H26="","",IFERROR(VLOOKUP($H26,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H26="","",IFERROR(VLOOKUP($H26,PQ_Diario!$A:$D,4,0),X26))</f>
         <v/>
       </c>
       <c r="S26" s="19" t="n">
@@ -2290,6 +2290,15 @@
       </c>
       <c r="U26" s="19" t="n">
         <v>0.0725</v>
+      </c>
+      <c r="V26" s="20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W26" s="20" t="n">
+        <v>113.98</v>
+      </c>
+      <c r="X26" s="20" t="n">
+        <v>211.88</v>
       </c>
     </row>
     <row r="27">
@@ -6038,7 +6047,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6093,7 +6102,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>114.5</v>
+        <v>113.63</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6124,7 +6133,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>110.35</v>
+        <v>110</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6155,7 +6164,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>114.78</v>
+        <v>114.98</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6186,7 +6195,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>112.45</v>
+        <v>112.75</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6217,7 +6226,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>96.56</v>
+        <v>97.81</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6248,7 +6257,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>91.40000000000001</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6274,7 +6283,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>112.5</v>
+        <v>112.55</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6300,7 +6309,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>90</v>
+        <v>91.25</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6326,7 +6335,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>49.74</v>
+        <v>50</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6352,7 +6361,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>72.34999999999999</v>
+        <v>73.75</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>2</v>
@@ -6378,7 +6387,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>73.09</v>
+        <v>76.36</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6404,7 +6413,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>64.86</v>
+        <v>65.11</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6430,7 +6439,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>41.8</v>
+        <v>42.05</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6456,7 +6465,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>71.25</v>
+        <v>72.8</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6482,7 +6491,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>57.75</v>
+        <v>58</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6508,7 +6517,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>53.4</v>
+        <v>53.5</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2330,15 +2330,15 @@
         <v/>
       </c>
       <c r="I27" s="17">
-        <f>IF($H27="","",IFERROR(VLOOKUP($H27,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H27="","",IFERROR(VLOOKUP($H27,PQ_Diario!$A:$D,2,0),V27))</f>
         <v/>
       </c>
       <c r="J27" s="17">
-        <f>IF($H27="","",IFERROR(VLOOKUP($H27,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H27="","",IFERROR(VLOOKUP($H27,PQ_Diario!$A:$D,3,0),W27))</f>
         <v/>
       </c>
       <c r="K27" s="17">
-        <f>IF($H27="","",IFERROR(VLOOKUP($H27,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H27="","",IFERROR(VLOOKUP($H27,PQ_Diario!$A:$D,4,0),X27))</f>
         <v/>
       </c>
       <c r="S27" s="19" t="n">
@@ -2349,6 +2349,15 @@
       </c>
       <c r="U27" s="19" t="n">
         <v>0.0595</v>
+      </c>
+      <c r="V27" s="20" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="W27" s="20" t="n">
+        <v>94.56999999999999</v>
+      </c>
+      <c r="X27" s="20" t="n">
+        <v>188</v>
       </c>
     </row>
     <row r="28">
@@ -6047,7 +6056,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6102,7 +6111,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>113.63</v>
+        <v>117.55</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6133,7 +6142,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6164,7 +6173,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>114.98</v>
+        <v>115.96</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6195,7 +6204,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>112.75</v>
+        <v>115.96</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6283,7 +6292,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>112.55</v>
+        <v>115.3</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6309,7 +6318,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>91.25</v>
+        <v>95</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6335,7 +6344,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>50</v>
+        <v>51.5</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6361,7 +6370,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>73.75</v>
+        <v>74.73</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>2</v>
@@ -6387,7 +6396,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>76.36</v>
+        <v>75.38</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6413,7 +6422,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>65.11</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6439,7 +6448,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>42.05</v>
+        <v>42.65</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6465,7 +6474,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>72.8</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6491,7 +6500,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>58</v>
+        <v>58.6</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6517,7 +6526,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>53.5</v>
+        <v>53.8</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2389,15 +2389,15 @@
         <v/>
       </c>
       <c r="I28" s="17">
-        <f>IF($H28="","",IFERROR(VLOOKUP($H28,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H28="","",IFERROR(VLOOKUP($H28,PQ_Diario!$A:$D,2,0),V28))</f>
         <v/>
       </c>
       <c r="J28" s="17">
-        <f>IF($H28="","",IFERROR(VLOOKUP($H28,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H28="","",IFERROR(VLOOKUP($H28,PQ_Diario!$A:$D,3,0),W28))</f>
         <v/>
       </c>
       <c r="K28" s="17">
-        <f>IF($H28="","",IFERROR(VLOOKUP($H28,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H28="","",IFERROR(VLOOKUP($H28,PQ_Diario!$A:$D,4,0),X28))</f>
         <v/>
       </c>
       <c r="S28" s="19" t="n">
@@ -2408,6 +2408,15 @@
       </c>
       <c r="U28" s="19" t="n">
         <v>0.09408999999999999</v>
+      </c>
+      <c r="V28" s="20" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="W28" s="20" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="X28" s="20" t="n">
+        <v>166.93</v>
       </c>
     </row>
     <row r="29">
@@ -6056,7 +6065,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6111,7 +6120,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>117.55</v>
+        <v>117.6</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6142,7 +6151,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>114</v>
+        <v>115.5</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6173,7 +6182,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>115.96</v>
+        <v>118.07</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6204,7 +6213,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>115.96</v>
+        <v>118.07</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6235,7 +6244,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>97.81</v>
+        <v>99.28</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6266,7 +6275,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>92.65000000000001</v>
+        <v>94.12</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6292,7 +6301,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>115.3</v>
+        <v>117.2</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6318,7 +6327,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>95</v>
+        <v>96.47</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6344,7 +6353,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>51.5</v>
+        <v>52.93</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6370,7 +6379,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>74.73</v>
+        <v>75.83</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>2</v>
@@ -6396,7 +6405,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>75.38</v>
+        <v>76</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6422,7 +6431,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>65.70999999999999</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6448,7 +6457,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>42.65</v>
+        <v>43.2</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6474,7 +6483,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>74.09999999999999</v>
+        <v>75.25</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6500,7 +6509,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>58.6</v>
+        <v>59.15</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6526,7 +6535,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>53.8</v>
+        <v>54.17</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>
